--- a/results/loeo/LOEO_결과.xlsx
+++ b/results/loeo/LOEO_결과.xlsx
@@ -714,10 +714,10 @@
         <v>0.1343</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7768</v>
+        <v>0.7812</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8219</v>
+        <v>0.8226</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -764,19 +764,19 @@
         <v>0.766</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8</v>
+        <v>0.8008</v>
       </c>
       <c r="I6" t="n">
         <v>0.7969000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1955</v>
+        <v>0.1957</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7755</v>
+        <v>0.7796</v>
       </c>
       <c r="L6" t="n">
-        <v>0.821</v>
+        <v>0.8226</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -823,23 +823,23 @@
         <v>0.822</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7937</v>
+        <v>0.7929</v>
       </c>
       <c r="I7" t="n">
         <v>0.7969000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1426</v>
+        <v>0.1425</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7768</v>
+        <v>0.7806</v>
       </c>
       <c r="L7" t="n">
-        <v>0.822</v>
+        <v>0.8227</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>5회차 평균 (회차 범위 0.7766~0.7771)</t>
+          <t>5회차 평균 (회차 범위 0.7806~0.7806)</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -882,23 +882,23 @@
         <v>0.8154</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8008</v>
+        <v>0.8</v>
       </c>
       <c r="I8" t="n">
         <v>0.7969000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1458</v>
+        <v>0.1457</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7764</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8222</v>
+        <v>0.8229</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>5회차 평균 (회차 범위 0.7762~0.7766)</t>
+          <t>5회차 평균 (회차 범위 0.7787~0.7803)</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -941,23 +941,23 @@
         <v>0.822</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7921</v>
+        <v>0.7905</v>
       </c>
       <c r="I9" t="n">
         <v>0.7969000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1424</v>
+        <v>0.1423</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7769</v>
+        <v>0.7806</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8219</v>
+        <v>0.8226</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>5회차 평균 (회차 범위 0.7768~0.7771)</t>
+          <t>5회차 평균 (회차 범위 0.7806~0.7806)</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -974,7 +974,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B0-log</t>
+          <t>B0-logit</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>(추가) B0를 기존 브랜치의 log(pi) 링크로</t>
+          <t>(민감도) B0를 지시서 §2-1 B 표기인 logit(pi) 링크로</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1009,10 +1009,10 @@
         <v>0.1343</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7812</v>
+        <v>0.7768</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8226</v>
+        <v>0.8219</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B2-log</t>
+          <t>B2-logit</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>(추가) B2를 기존 브랜치의 log(pi) 링크로</t>
+          <t>(민감도) B2를 지시서 §2-1 B 표기인 logit(pi) 링크로</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1059,23 +1059,23 @@
         <v>0.822</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7929</v>
+        <v>0.7937</v>
       </c>
       <c r="I11" t="n">
         <v>0.7969000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1425</v>
+        <v>0.1426</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7806</v>
+        <v>0.7768</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8227</v>
+        <v>0.822</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>5회차 평균 (회차 범위 0.7806~0.7806)</t>
+          <t>5회차 평균 (회차 범위 0.7766~0.7771)</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>실패 (B2-log 0.8507 ≤ B0-log 0.8550)</t>
+          <t>실패 (B2-logit 0.8507 ≤ B0-logit 0.8550)</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>6382.361</v>
+        <v>6382.3108</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --fix-b --out results/loeo/B0</t>
+          <t>train.py --prior-family area --area-link log --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --fix-b --out results/loeo/B0</t>
         </is>
       </c>
     </row>
@@ -2116,16 +2116,16 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8</v>
+        <v>0.8008</v>
       </c>
       <c r="J10" t="n">
         <v>0.7889</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.8135</v>
+        <v>-0.8095</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4433</v>
+        <v>0.4451</v>
       </c>
       <c r="M10" t="n">
         <v>-1.9754</v>
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>6360.1593</v>
+        <v>6360.1145</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --out results/loeo/B1</t>
+          <t>train.py --prior-family area --area-link log --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --out results/loeo/B1</t>
         </is>
       </c>
     </row>
@@ -2186,13 +2186,13 @@
         <v>0.9407</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.0271</v>
+        <v>-0.0254</v>
       </c>
       <c r="L11" t="n">
-        <v>0.9733000000000001</v>
+        <v>0.975</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0063</v>
+        <v>-0.0022</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -2200,17 +2200,17 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>6379.3115</v>
+        <v>6379.2436</v>
       </c>
       <c r="P11" t="n">
-        <v>29.5981</v>
+        <v>29.5963</v>
       </c>
       <c r="Q11" t="n">
         <v>46</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2000 돗토리 --out results/loeo/B2/2000 돗토리</t>
+          <t>train.py --prior-family area --area-link log --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2000 돗토리 --out results/loeo/B2/2000 돗토리</t>
         </is>
       </c>
     </row>
@@ -2250,13 +2250,13 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1921</v>
+        <v>-0.1898</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8252</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.313</v>
+        <v>-0.3082</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -2264,17 +2264,17 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>6377.1034</v>
+        <v>6377.0506</v>
       </c>
       <c r="P12" t="n">
-        <v>35.2704</v>
+        <v>35.2689</v>
       </c>
       <c r="Q12" t="n">
         <v>46</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2004 니가타현주에쓰 --out results/loeo/B2/2004 니가타현주에쓰</t>
+          <t>train.py --prior-family area --area-link log --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2004 니가타현주에쓰 --out results/loeo/B2/2004 니가타현주에쓰</t>
         </is>
       </c>
     </row>
@@ -2314,13 +2314,13 @@
         <v>0.8333</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.4098</v>
+        <v>-0.407</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6637999999999999</v>
+        <v>0.6656</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.5618</v>
+        <v>-0.5571</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -2328,17 +2328,17 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>6374.7158</v>
+        <v>6374.6712</v>
       </c>
       <c r="P13" t="n">
-        <v>30.7964</v>
+        <v>30.8054</v>
       </c>
       <c r="Q13" t="n">
         <v>46</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2016 구마모토 --out results/loeo/B2/2016 구마모토</t>
+          <t>train.py --prior-family area --area-link log --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2016 구마모토 --out results/loeo/B2/2016 구마모토</t>
         </is>
       </c>
     </row>
@@ -2378,13 +2378,13 @@
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2683</v>
+        <v>-0.2655</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7647</v>
+        <v>0.7668</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.5535</v>
+        <v>-0.5481</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -2392,17 +2392,17 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>6374.8946</v>
+        <v>6374.8558</v>
       </c>
       <c r="P14" t="n">
-        <v>36.4539</v>
+        <v>36.4608</v>
       </c>
       <c r="Q14" t="n">
         <v>46</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2018 오사카 --out results/loeo/B2/2018 오사카</t>
+          <t>train.py --prior-family area --area-link log --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2018 오사카 --out results/loeo/B2/2018 오사카</t>
         </is>
       </c>
     </row>
@@ -2442,13 +2442,13 @@
         <v>0.5278</v>
       </c>
       <c r="K15" t="n">
-        <v>0.156</v>
+        <v>0.1583</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1688</v>
+        <v>1.1716</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.064</v>
+        <v>-0.059</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -2456,17 +2456,17 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>6378.8086</v>
+        <v>6378.7491</v>
       </c>
       <c r="P15" t="n">
-        <v>28.3795</v>
+        <v>28.3695</v>
       </c>
       <c r="Q15" t="n">
         <v>46</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2018 훗카이도 --out results/loeo/B2/2018 훗카이도</t>
+          <t>train.py --prior-family area --area-link log --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2018 훗카이도 --out results/loeo/B2/2018 훗카이도</t>
         </is>
       </c>
     </row>
@@ -2506,13 +2506,13 @@
         <v>0.9481000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.285</v>
+        <v>-0.2813</v>
       </c>
       <c r="L16" t="n">
-        <v>0.752</v>
+        <v>0.7548</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.735</v>
+        <v>-0.7285</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -2520,17 +2520,17 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>6371.2565</v>
+        <v>6371.2274</v>
       </c>
       <c r="P16" t="n">
-        <v>32.6252</v>
+        <v>32.6024</v>
       </c>
       <c r="Q16" t="n">
         <v>46</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 1 --test-event 2000 돗토리 --out results/loeo/B2-w1/2000 돗토리</t>
+          <t>train.py --prior-family area --area-link log --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 1 --test-event 2000 돗토리 --out results/loeo/B2-w1/2000 돗토리</t>
         </is>
       </c>
     </row>
@@ -2570,13 +2570,13 @@
         <v>0.75</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3698</v>
+        <v>-0.3658</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6909</v>
+        <v>0.6936</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8875999999999999</v>
+        <v>-0.8808</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -2584,17 +2584,17 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>6369.8575</v>
+        <v>6369.8387</v>
       </c>
       <c r="P17" t="n">
-        <v>37.8781</v>
+        <v>37.8585</v>
       </c>
       <c r="Q17" t="n">
         <v>46</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 1 --test-event 2004 니가타현주에쓰 --out results/loeo/B2-w1/2004 니가타현주에쓰</t>
+          <t>train.py --prior-family area --area-link log --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 1 --test-event 2004 니가타현주에쓰 --out results/loeo/B2-w1/2004 니가타현주에쓰</t>
         </is>
       </c>
     </row>
@@ -2634,13 +2634,13 @@
         <v>0.7949000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.4817</v>
+        <v>-0.4777</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6177</v>
+        <v>0.6202</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1193</v>
+        <v>-1.1132</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -2648,17 +2648,17 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>6367.4009</v>
+        <v>6367.3811</v>
       </c>
       <c r="P18" t="n">
-        <v>33.4934</v>
+        <v>33.489</v>
       </c>
       <c r="Q18" t="n">
         <v>46</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 1 --test-event 2016 구마모토 --out results/loeo/B2-w1/2016 구마모토</t>
+          <t>train.py --prior-family area --area-link log --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 1 --test-event 2016 구마모토 --out results/loeo/B2-w1/2016 구마모토</t>
         </is>
       </c>
     </row>
@@ -2698,13 +2698,13 @@
         <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3977</v>
+        <v>-0.3936</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6719000000000001</v>
+        <v>0.6746</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0461</v>
+        <v>-1.0393</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -2712,17 +2712,17 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>6368.3652</v>
+        <v>6368.3505</v>
       </c>
       <c r="P19" t="n">
-        <v>38.7606</v>
+        <v>38.7539</v>
       </c>
       <c r="Q19" t="n">
         <v>46</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 1 --test-event 2018 오사카 --out results/loeo/B2-w1/2018 오사카</t>
+          <t>train.py --prior-family area --area-link log --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 1 --test-event 2018 오사카 --out results/loeo/B2-w1/2018 오사카</t>
         </is>
       </c>
     </row>
@@ -2762,13 +2762,13 @@
         <v>0.5556</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1398</v>
+        <v>-0.1344</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8695000000000001</v>
+        <v>0.8742</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7107</v>
+        <v>-0.7023</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2776,17 +2776,17 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>6371.6902</v>
+        <v>6371.6774</v>
       </c>
       <c r="P20" t="n">
-        <v>30.9053</v>
+        <v>30.8683</v>
       </c>
       <c r="Q20" t="n">
         <v>46</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 1 --test-event 2018 훗카이도 --out results/loeo/B2-w1/2018 훗카이도</t>
+          <t>train.py --prior-family area --area-link log --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 1 --test-event 2018 훗카이도 --out results/loeo/B2-w1/2018 훗카이도</t>
         </is>
       </c>
     </row>
@@ -2826,13 +2826,13 @@
         <v>0.9407</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.0218</v>
+        <v>-0.0204</v>
       </c>
       <c r="L21" t="n">
-        <v>0.9784</v>
+        <v>0.9799</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0907</v>
+        <v>0.0944</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2840,17 +2840,17 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>6381.0556</v>
+        <v>6380.9945</v>
       </c>
       <c r="P21" t="n">
-        <v>29.5133</v>
+        <v>29.512</v>
       </c>
       <c r="Q21" t="n">
         <v>46</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 10 --test-event 2000 돗토리 --out results/loeo/B2-w10/2000 돗토리</t>
+          <t>train.py --prior-family area --area-link log --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 10 --test-event 2000 돗토리 --out results/loeo/B2-w10/2000 돗토리</t>
         </is>
       </c>
     </row>
@@ -2890,13 +2890,13 @@
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1845</v>
+        <v>-0.1825</v>
       </c>
       <c r="L22" t="n">
-        <v>0.8315</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2259</v>
+        <v>-0.2215</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -2904,17 +2904,17 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>6378.7853</v>
+        <v>6378.7372</v>
       </c>
       <c r="P22" t="n">
-        <v>35.1804</v>
+        <v>35.1795</v>
       </c>
       <c r="Q22" t="n">
         <v>46</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 10 --test-event 2004 니가타현주에쓰 --out results/loeo/B2-w10/2004 니가타현주에쓰</t>
+          <t>train.py --prior-family area --area-link log --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 10 --test-event 2004 니가타현주에쓰 --out results/loeo/B2-w10/2004 니가타현주에쓰</t>
         </is>
       </c>
     </row>
@@ -2954,13 +2954,13 @@
         <v>0.8333</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.4252</v>
+        <v>-0.4226</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6536</v>
+        <v>0.6553</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.4589</v>
+        <v>-0.4545</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -2968,17 +2968,17 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>6376.6375</v>
+        <v>6376.5943</v>
       </c>
       <c r="P23" t="n">
-        <v>30.6637</v>
+        <v>30.6733</v>
       </c>
       <c r="Q23" t="n">
         <v>46</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 10 --test-event 2016 구마모토 --out results/loeo/B2-w10/2016 구마모토</t>
+          <t>train.py --prior-family area --area-link log --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 10 --test-event 2016 구마모토 --out results/loeo/B2-w10/2016 구마모토</t>
         </is>
       </c>
     </row>
@@ -3018,13 +3018,13 @@
         <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.2675</v>
+        <v>-0.265</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7653</v>
+        <v>0.7672</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4681</v>
+        <v>-0.4631</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -3032,17 +3032,17 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>6376.5408</v>
+        <v>6376.5056</v>
       </c>
       <c r="P24" t="n">
-        <v>36.3552</v>
+        <v>36.3627</v>
       </c>
       <c r="Q24" t="n">
         <v>46</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 10 --test-event 2018 오사카 --out results/loeo/B2-w10/2018 오사카</t>
+          <t>train.py --prior-family area --area-link log --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 10 --test-event 2018 오사카 --out results/loeo/B2-w10/2018 오사카</t>
         </is>
       </c>
     </row>
@@ -3082,13 +3082,13 @@
         <v>0.5278</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1672</v>
+        <v>0.1692</v>
       </c>
       <c r="L25" t="n">
-        <v>1.182</v>
+        <v>1.1844</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0187</v>
+        <v>0.0233</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -3096,24 +3096,24 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>6380.3884</v>
+        <v>6380.336</v>
       </c>
       <c r="P25" t="n">
-        <v>28.3153</v>
+        <v>28.3058</v>
       </c>
       <c r="Q25" t="n">
         <v>46</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 10 --test-event 2018 훗카이도 --out results/loeo/B2-w10/2018 훗카이도</t>
+          <t>train.py --prior-family area --area-link log --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 10 --test-event 2018 훗카이도 --out results/loeo/B2-w10/2018 훗카이도</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B0-log</t>
+          <t>B0-logit</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>6382.3108</v>
+        <v>6382.361</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -3176,14 +3176,14 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --fix-b --area-link log --out results/loeo/B0-log</t>
+          <t>train.py --prior-family area --area-link logit --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --fix-b --out results/loeo/B0-logit</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B2-log</t>
+          <t>B2-logit</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -3216,13 +3216,13 @@
         <v>0.9407</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.0254</v>
+        <v>-0.0271</v>
       </c>
       <c r="L27" t="n">
-        <v>0.975</v>
+        <v>0.9733000000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.0022</v>
+        <v>-0.0063</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -3230,24 +3230,24 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>6379.2436</v>
+        <v>6379.3115</v>
       </c>
       <c r="P27" t="n">
-        <v>29.5963</v>
+        <v>29.5981</v>
       </c>
       <c r="Q27" t="n">
         <v>46</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2000 돗토리 --area-link log --out results/loeo/B2-log/2000 돗토리</t>
+          <t>train.py --prior-family area --area-link logit --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2000 돗토리 --out results/loeo/B2-logit/2000 돗토리</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B2-log</t>
+          <t>B2-logit</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -3280,13 +3280,13 @@
         <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.1898</v>
+        <v>-0.1921</v>
       </c>
       <c r="L28" t="n">
-        <v>0.8270999999999999</v>
+        <v>0.8252</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.3082</v>
+        <v>-0.313</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -3294,24 +3294,24 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>6377.0506</v>
+        <v>6377.1034</v>
       </c>
       <c r="P28" t="n">
-        <v>35.2689</v>
+        <v>35.2704</v>
       </c>
       <c r="Q28" t="n">
         <v>46</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2004 니가타현주에쓰 --area-link log --out results/loeo/B2-log/2004 니가타현주에쓰</t>
+          <t>train.py --prior-family area --area-link logit --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2004 니가타현주에쓰 --out results/loeo/B2-logit/2004 니가타현주에쓰</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B2-log</t>
+          <t>B2-logit</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -3344,13 +3344,13 @@
         <v>0.8333</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.407</v>
+        <v>-0.4098</v>
       </c>
       <c r="L29" t="n">
-        <v>0.6656</v>
+        <v>0.6637999999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.5571</v>
+        <v>-0.5618</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -3358,24 +3358,24 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>6374.6712</v>
+        <v>6374.7158</v>
       </c>
       <c r="P29" t="n">
-        <v>30.8054</v>
+        <v>30.7964</v>
       </c>
       <c r="Q29" t="n">
         <v>46</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2016 구마모토 --area-link log --out results/loeo/B2-log/2016 구마모토</t>
+          <t>train.py --prior-family area --area-link logit --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2016 구마모토 --out results/loeo/B2-logit/2016 구마모토</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B2-log</t>
+          <t>B2-logit</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -3408,13 +3408,13 @@
         <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.2655</v>
+        <v>-0.2683</v>
       </c>
       <c r="L30" t="n">
-        <v>0.7668</v>
+        <v>0.7647</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.5481</v>
+        <v>-0.5535</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -3422,24 +3422,24 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>6374.8558</v>
+        <v>6374.8946</v>
       </c>
       <c r="P30" t="n">
-        <v>36.4608</v>
+        <v>36.4539</v>
       </c>
       <c r="Q30" t="n">
         <v>46</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2018 오사카 --area-link log --out results/loeo/B2-log/2018 오사카</t>
+          <t>train.py --prior-family area --area-link logit --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2018 오사카 --out results/loeo/B2-logit/2018 오사카</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B2-log</t>
+          <t>B2-logit</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -3472,13 +3472,13 @@
         <v>0.5278</v>
       </c>
       <c r="K31" t="n">
-        <v>0.1583</v>
+        <v>0.156</v>
       </c>
       <c r="L31" t="n">
-        <v>1.1716</v>
+        <v>1.1688</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.059</v>
+        <v>-0.064</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -3486,17 +3486,17 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>6378.7491</v>
+        <v>6378.8086</v>
       </c>
       <c r="P31" t="n">
-        <v>28.3695</v>
+        <v>28.3795</v>
       </c>
       <c r="Q31" t="n">
         <v>46</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2018 훗카이도 --area-link log --out results/loeo/B2-log/2018 훗카이도</t>
+          <t>train.py --prior-family area --area-link logit --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2018 훗카이도 --out results/loeo/B2-logit/2018 훗카이도</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B0-log</t>
+          <t>B0-logit</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B2-log</t>
+          <t>B2-logit</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>B0-log</t>
+          <t>B0-logit</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>B2-log</t>
+          <t>B2-logit</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>B0-log</t>
+          <t>B0-logit</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>B2-log</t>
+          <t>B2-logit</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>B0-log</t>
+          <t>B0-logit</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>B2-log</t>
+          <t>B2-logit</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>B0-log</t>
+          <t>B0-logit</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>B2-log</t>
+          <t>B2-logit</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -5380,7 +5380,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B2-log − B0-log</t>
+          <t>B2-logit − B0-logit</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5410,7 +5410,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B2-log − B0-log</t>
+          <t>B2-logit − B0-logit</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5607,7 +5607,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B0-log LS 사후 가중</t>
+          <t>B0-logit LS 사후 가중</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>같은 기준값을 기존 브랜치 링크(log)로</t>
+          <t>같은 기준값을 지시서 §2-1 B 표기(logit) 링크로</t>
         </is>
       </c>
     </row>
@@ -5735,7 +5735,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>followup3-loeo</t>
+          <t>claude/vigilant-wozniak-atum1b</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -5757,7 +5757,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0c824047f9c18d2672ba2c2c26287edb60f05781</t>
+          <t>396d2b3f3e9dd7cd27e8f938c33ca5546c7f2f8f</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -5779,8 +5779,227 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M score_loeo.py
-?? results/</t>
+          <t>M prior.py
+ D results/loeo/B0-log/eval_detail.csv
+ D results/loeo/B0-log/eval_per_event.csv
+ D results/loeo/B0-log/eval_scores.csv
+ D results/loeo/B0-log/eval_summary.csv
+ D results/loeo/B0-log/loss_curve.png
+ D results/loeo/B0-log/loss_history.csv
+ D results/loeo/B0-log/params.csv
+ D results/loeo/B0-log/predictions.csv
+ D results/loeo/B0-log/run_meta.json
+ M results/loeo/B0/eval_detail.csv
+ M results/loeo/B0/eval_per_event.csv
+ M results/loeo/B0/eval_scores.csv
+ M results/loeo/B0/eval_summary.csv
+ M results/loeo/B0/loss_curve.png
+ M results/loeo/B0/loss_history.csv
+ M results/loeo/B0/params.csv
+ M results/loeo/B0/predictions.csv
+ M results/loeo/B0/run_meta.json
+ M results/loeo/B1/eval_detail.csv
+ M results/loeo/B1/eval_per_event.csv
+ M results/loeo/B1/eval_scores.csv
+ M results/loeo/B1/eval_summary.csv
+ M results/loeo/B1/loss_curve.png
+ M results/loeo/B1/loss_history.csv
+ M results/loeo/B1/params.csv
+ M results/loeo/B1/predictions.csv
+ M results/loeo/B1/run_meta.json
+ D "results/loeo/B2-log/2000 \353\217\227\355\206\240\353\246\254/eval_detail.csv"
+ D "results/loeo/B2-log/2000 \353\217\227\355\206\240\353\246\254/eval_per_event.csv"
+ D "results/loeo/B2-log/2000 \353\217\227\355\206\240\353\246\254/eval_scores.csv"
+ D "results/loeo/B2-log/2000 \353\217\227\355\206\240\353\246\254/eval_summary.csv"
+ D "results/loeo/B2-log/2000 \353\217\227\355\206\240\353\246\254/loss_curve.png"
+ D "results/loeo/B2-log/2000 \353\217\227\355\206\240\353\246\254/loss_history.csv"
+ D "results/loeo/B2-log/2000 \353\217\227\355\206\240\353\246\254/params.csv"
+ D "results/loeo/B2-log/2000 \353\217\227\355\206\240\353\246\254/predictions.csv"
+ D "results/loeo/B2-log/2000 \353\217\227\355\206\240\353\246\254/run_meta.json"
+ D "results/loeo/B2-log/2004 \353\213\210\352\260\200\355\203\200\355\230\204\354\243\274\354\227\220\354\223\260/eval_detail.csv"
+ D "results/loeo/B2-log/2004 \353\213\210\352\260\200\355\203\200\355\230\204\354\243\274\354\227\220\354\223\260/eval_per_event.csv"
+ D "results/loeo/B2-log/2004 \353\213\210\352\260\200\355\203\200\355\230\204\354\243\274\354\227\220\354\223\260/eval_scores.csv"
+ D "results/loeo/B2-log/2004 \353\213\210\352\260\200\355\203\200\355\230\204\354\243\274\354\227\220\354\223\260/eval_summary.csv"
+ D "results/loeo/B2-log/2004 \353\213\210\352\260\200\355\203\200\355\230\204\354\243\274\354\227\220\354\223\260/loss_curve.png"
+ D "results/loeo/B2-log/2004 \353\213\210\352\260\200\355\203\200\355\230\204\354\243\274\354\227\220\354\223\260/loss_history.csv"
+ D "results/loeo/B2-log/2004 \353\213\210\352\260\200\355\203\200\355\230\204\354\243\274\354\227\220\354\223\260/params.csv"
+ D "results/loeo/B2-log/2004 \353\213\210\352\260\200\355\203\200\355\230\204\354\243\274\354\227\220\354\223\260/predictions.csv"
+ D "results/loeo/B2-log/2004 \353\213\210\352\260\200\355\203\200\355\230\204\354\243\274\354\227\220\354\223\260/run_meta.json"
+ D "results/loeo/B2-log/2016 \352\265\254\353\247\210\353\252\250\355\206\240/eval_detail.csv"
+ D "results/loeo/B2-log/2016 \352\265\254\353\247\210\353\252\250\355\206\240/eval_per_event.csv"
+ D "results/loeo/B2-log/2016 \352\265\254\353\247\210\353\252\250\355\206\240/eval_scores.csv"
+ D "results/loeo/B2-log/2016 \352\265\254\353\247\210\353\252\250\355\206\240/eval_summary.csv"
+ D "results/loeo/B2-log/2016 \352\265\254\353\247\210\353\252\250\355\206\240/loss_curve.png"
+ D "results/loeo/B2-log/2016 \352\265\254\353\247\210\353\252\250\355\206\240/loss_history.csv"
+ D "results/loeo/B2-log/2016 \352\265\254\353\247\210\353\252\250\355\206\240/params.csv"
+ D "results/loeo/B2-log/2016 \352\265\254\353\247\210\353\252\250\355\206\240/predictions.csv"
+ D "results/loeo/B2-log/2016 \352\265\254\353\247\210\353\252\250\355\206\240/run_meta.json"
+ D "results/loeo/B2-log/2018 \354\230\244\354\202\254\354\271\264/eval_detail.csv"
+ D "results/loeo/B2-log/2018 \354\230\244\354\202\254\354\271\264/eval_per_event.csv"
+ D "results/loeo/B2-log/2018 \354\230\244\354\202\254\354\271\264/eval_scores.csv"
+ D "results/loeo/B2-log/2018 \354\230\244\354\202\254\354\271\264/eval_summary.csv"
+ D "results/loeo/B2-log/2018 \354\230\244\354\202\254\354\271\264/loss_curve.png"
+ D "results/loeo/B2-log/2018 \354\230\244\354\202\254\354\271\264/loss_history.csv"
+ D "results/loeo/B2-log/2018 \354\230\244\354\202\254\354\271\264/params.csv"
+ D "results/loeo/B2-log/2018 \354\230\244\354\202\254\354\271\264/predictions.csv"
+ D "results/loeo/B2-log/2018 \354\230\244\354\202\254\354\271\264/run_meta.json"
+ D "results/loeo/B2-log/2018 \355\233\227\354\271\264\354\235\264\353\217\204/eval_detail.csv"
+ D "results/loeo/B2-log/2018 \355\233\227\354\271\264\354\235\264\353\217\204/eval_per_event.csv"
+ D "results/loeo/B2-log/2018 \355\233\227\354\271\264\354\235\264\353\217\204/eval_scores.csv"
+ D "results/loeo/B2-log/2018 \355\233\227\354\271\264\354\235\264\353\217\204/eval_summary.csv"
+ D "results/loeo/B2-log/2018 \355\233\227\354\271\264\354\235\264\353\217\204/loss_curve.png"
+ D "results/loeo/B2-log/2018 \355\233\227\354\271\264\354\235\264\353\217\204/loss_history.csv"
+ D "results/loeo/B2-log/2018 \355\233\227\354\271\264\354\235\264\353\217\204/params.csv"
+ D "results/loeo/B2-log/2018 \355\233\227\354\271\264\354\235\264\353\217\204/predictions.csv"
+ D "results/loeo/B2-log/2018 \355\233\227\354\271\264\354\235\264\353\217\204/run_meta.json"
+ M "results/loeo/B2-w1/2000 \353\217\227\355\206\240\353\246\254/eval_detail.csv"
+ M "results/loeo/B2-w1/2000 \353\217\227\355\206\240\353\246\254/eval_per_event.csv"
+ M "results/loeo/B2-w1/2000 \353\217\227\355\206\240\353\246\254/eval_scores.csv"
+ M "results/loeo/B2-w1/2000 \353\217\227\355\206\240\353\246\254/eval_summary.csv"
+ M "results/loeo/B2-w1/2000 \353\217\227\355\206\240\353\246\254/loss_curve.png"
+ M "results/loeo/B2-w1/2000 \353\217\227\355\206\240\353\246\254/loss_history.csv"
+ M "results/loeo/B2-w1/2000 \353\217\227\355\206\240\353\246\254/params.csv"
+ M "results/loeo/B2-w1/2000 \353\217\227\355\206\240\353\246\254/predictions.csv"
+ M "results/loeo/B2-w1/2000 \353\217\227\355\206\240\353\246\254/run_meta.json"
+ M "results/loeo/B2-w1/2004 \353\213\210\352\260\200\355\203\200\355\230\204\354\243\274\354\227\220\354\223\260/eval_detail.csv"
+ M "results/loeo/B2-w1/2004 \353\213\210\352\260\200\355\203\200\355\230\204\354\243\274\354\227\220\354\223\260/eval_per_event.csv"
+ M "results/loeo/B2-w1/2004 \353\213\210\352\260\200\355\203\200\355\230\204\354\243\274\354\227\220\354\223\260/eval_scores.csv"
+ M "results/loeo/B2-w1/2004 \353\213\210\352\260\200\355\203\200\355\230\204\354\243\274\354\227\220\354\223\260/eval_summary.csv"
+ M "results/loeo/B2-w1/2004 \353\213\210\352\260\200\355\203\200\355\230\204\354\243\274\354\227\220\354\223\260/loss_curve.png"
+ M "results/loeo/B2-w1/2004 \353\213\210\352\260\200\355\203\200\355\230\204\354\243\274\354\227\220\354\223\260/loss_history.csv"
+ M "results/loeo/B2-w1/2004 \353\213\210\352\260\200\355\203\200\355\230\204\354\243\274\354\227\220\354\223\260/params.csv"
+ M "results/loeo/B2-w1/2004 \353\213\210\352\260\200\355\203\200\355\230\204\354\243\274\354\227\220\354\223\260/predictions.csv"
+ M "results/loeo/B2-w1/2004 \353\213\210\352\260\200\355\203\200\355\230\204\354\243\274\354\227\220\354\223\260/run_meta.json"
+ M "results/loeo/B2-w1/2016 \352\265\254\353\247\210\353\252\250\355\206\240/eval_detail.csv"
+ M "results/loeo/B2-w1/2016 \352\265\254\353\247\210\353\252\250\355\206\240/eval_per_event.csv"
+ M "results/loeo/B2-w1/2016 \352\265\254\353\247\210\353\252\250\355\206\240/eval_scores.csv"
+ M "results/loeo/B2-w1/2016 \352\265\254\353\247\210\353\252\250\355\206\240/eval_summary.csv"
+ M "results/loeo/B2-w1/2016 \352\265\254\353\247\210\353\252\250\355\206\240/loss_curve.png"
+ M "results/loeo/B2-w1/2016 \352\265\254\353\247\210\353\252\250\355\206\240/loss_history.csv"
+ M "results/loeo/B2-w1/2016 \352\265\254\353\247\210\353\252\250\355\206\240/params.csv"
+ M "results/loeo/B2-w1/2016 \352\265\254\353\247\210\353\252\250\355\206\240/predictions.csv"
+ M "results/loeo/B2-w1/2016 \352\265\254\353\247\210\353\252\250\355\206\240/run_meta.json"
+ M "results/loeo/B2-w1/2018 \354\230\244\354\202\254\354\271\264/eval_detail.csv"
+ M "results/loeo/B2-w1/2018 \354\230\244\354\202\254\354\271\264/eval_per_event.csv"
+ M "results/loeo/B2-w1/2018 \354\230\244\354\202\254\354\271\264/eval_scores.csv"
+ M "results/loeo/B2-w1/2018 \354\230\244\354\202\254\354\271\264/eval_summary.csv"
+ M "results/loeo/B2-w1/2018 \354\230\244\354\202\254\354\271\264/loss_curve.png"
+ M "results/loeo/B2-w1/2018 \354\230\244\354\202\254\354\271\264/loss_history.csv"
+ M "results/loeo/B2-w1/2018 \354\230\244\354\202\254\354\271\264/params.csv"
+ M "results/loeo/B2-w1/2018 \354\230\244\354\202\254\354\271\264/predictions.csv"
+ M "results/loeo/B2-w1/2018 \354\230\244\354\202\254\354\271\264/run_meta.json"
+ M "results/loeo/B2-w1/2018 \355\233\227\354\271\264\354\235\264\353\217\204/eval_detail.csv"
+ M "results/loeo/B2-w1/2018 \355\233\227\354\271\264\354\235\264\353\217\204/eval_per_event.csv"
+ M "results/loeo/B2-w1/2018 \355\233\227\354\271\264\354\235\264\353\217\204/eval_scores.csv"
+ M "results/loeo/B2-w1/2018 \355\233\227\354\271\264\354\235\264\353\217\204/eval_summary.csv"
+ M "results/loeo/B2-w1/2018 \355\233\227\354\271\264\354\235\264\353\217\204/loss_curve.png"
+ M "results/loeo/B2-w1/2018 \355\233\227\354\271\264\354\235\264\353\217\204/loss_history.csv"
+ M "results/loeo/B2-w1/2018 \355\233\227\354\271\264\354\235\264\353\217\204/params.csv"
+ M "results/loeo/B2-w1/2018 \355\233\227\354\271\264\354\235\264\353\217\204/predictions.csv"
+ M "results/loeo/B2-w1/2018 \355\233\227\354\271\264\354\235\264\353\217\204/run_meta.json"
+ M "results/loeo/B2-w10/2000 \353\217\227\355\206\240\353\246\254/eval_detail.csv"
+ M "results/loeo/B2-w10/2000 \353\217\227\355\206\240\353\246\254/eval_per_event.csv"
+ M "results/loeo/B2-w10/2000 \353\217\227\355\206\240\353\246\254/eval_scores.csv"
+ M "results/loeo/B2-w10/2000 \353\217\227\355\206\240\353\246\254/eval_summary.csv"
+ M "results/loeo/B2-w10/2000 \353\217\227\355\206\240\353\246\254/loss_curve.png"
+ M "results/loeo/B2-w10/2000 \353\217\227\355\206\240\353\246\254/loss_history.csv"
+ M "results/loeo/B2-w10/2000 \353\217\227\355\206\240\353\246\254/params.csv"
+ M "results/loeo/B2-w10/2000 \353\217\227\355\206\240\353\246\254/predictions.csv"
+ M "results/loeo/B2-w10/2000 \353\217\227\355\206\240\353\246\254/run_meta.json"
+ M "results/loeo/B2-w10/2004 \353\213\210\352\260\200\355\203\200\355\230\204\354\243\274\354\227\220\354\223\260/eval_detail.csv"
+ M "results/loeo/B2-w10/2004 \353\213\210\352\260\200\355\203\200\355\230\204\354\243\274\354\227\220\354\223\260/eval_per_event.csv"
+ M "results/loeo/B2-w10/2004 \353\213\210\352\260\200\355\203\200\355\230\204\354\243\274\354\227\220\354\223\260/eval_scores.csv"
+ M "results/loeo/B2-w10/2004 \353\213\210\352\260\200\355\203\200\355\230\204\354\243\274\354\227\220\354\223\260/eval_summary.csv"
+ M "results/loeo/B2-w10/2004 \353\213\210\352\260\200\355\203\200\355\230\204\354\243\274\354\227\220\354\223\260/loss_curve.png"
+ M "results/loeo/B2-w10/2004 \353\213\210\352\260\200\355\203\200\355\230\204\354\243\274\354\227\220\354\223\260/loss_history.csv"
+ M "results/loeo/B2-w10/2004 \353\213\210\352\260\200\355\203\200\355\230\204\354\243\274\354\227\220\354\223\260/params.csv"
+ M "results/loeo/B2-w10/2004 \353\213\210\352\260\200\355\203\200\355\230\204\354\243\274\354\227\220\354\223\260/predictions.csv"
+ M "results/loeo/B2-w10/2004 \353\213\210\352\260\200\355\203\200\355\230\204\354\243\274\354\227\220\354\223\260/run_meta.json"
+ M "results/loeo/B2-w10/2016 \352\265\254\353\247\210\353\252\250\355\206\240/eval_detail.csv"
+ M "results/loeo/B2-w10/2016 \352\265\254\353\247\210\353\252\250\355\206\240/eval_per_event.csv"
+ M "results/loeo/B2-w10/2016 \352\265\254\353\247\210\353\252\250\355\206\240/eval_scores.csv"
+ M "results/loeo/B2-w10/2016 \352\265\254\353\247\210\353\252\250\355\206\240/eval_summary.csv"
+ M "results/loeo/B2-w10/2016 \352\265\254\353\247\210\353\252\250\355\206\240/loss_curve.png"
+ M "results/loeo/B2-w10/2016 \352\265\254\353\247\210\353\252\250\355\206\240/loss_history.csv"
+ M "results/loeo/B2-w10/2016 \352\265\254\353\247\210\353\252\250\355\206\240/params.csv"
+ M "results/loeo/B2-w10/2016 \352\265\254\353\247\210\353\252\250\355\206\240/predictions.csv"
+ M "results/loeo/B2-w10/2016 \352\265\254\353\247\210\353\252\250\355\206\240/run_meta.json"
+ M "results/loeo/B2-w10/2018 \354\230\244\354\202\254\354\271\264/eval_detail.csv"
+ M "results/loeo/B2-w10/2018 \354\230\244\354\202\254\354\271\264/eval_per_event.csv"
+ M "results/loeo/B2-w10/2018 \354\230\244\354\202\254\354\271\264/eval_scores.csv"
+ M "results/loeo/B2-w10/2018 \354\230\244\354\202\254\354\271\264/eval_summary.csv"
+ M "results/loeo/B2-w10/2018 \354\230\244\354\202\254\354\271\264/loss_curve.png"
+ M "results/loeo/B2-w10/2018 \354\230\244\354\202\254\354\271\264/loss_history.csv"
+ M "results/loeo/B2-w10/2018 \354\230\244\354\202\254\354\271\264/params.csv"
+ M "results/loeo/B2-w10/2018 \354\230\244\354\202\254\354\271\264/predictions.csv"
+ M "results/loeo/B2-w10/2018 \354\230\244\354\202\254\354\271\264/run_meta.json"
+ M "results/loeo/B2-w10/2018 \355\233\227\354\271\264\354\235\264\353\217\204/eval_detail.csv"
+ M "results/loeo/B2-w10/2018 \355\233\227\354\271\264\354\235\264\353\217\204/eval_per_event.csv"
+ M "results/loeo/B2-w10/2018 \355\233\227\354\271\264\354\235\264\353\217\204/eval_scores.csv"
+ M "results/loeo/B2-w10/2018 \355\233\227\354\271\264\354\235\264\353\217\204/eval_summary.csv"
+ M "results/loeo/B2-w10/2018 \355\233\227\354\271\264\354\235\264\353\217\204/loss_curve.png"
+ M "results/loeo/B2-w10/2018 \355\233\227\354\271\264\354\235\264\353\217\204/loss_history.csv"
+ M "results/loeo/B2-w10/2018 \355\233\227\354\271\264\354\235\264\353\217\204/params.csv"
+ M "results/loeo/B2-w10/2018 \355\233\227\354\271\264\354\235\264\353\217\204/predictions.csv"
+ M "results/loeo/B2-w10/2018 \355\233\227\354\271\264\354\235\264\353\217\204/run_meta.json"
+ M "results/loeo/B2/2000 \353\217\227\355\206\240\353\246\254/eval_detail.csv"
+ M "results/loeo/B2/2000 \353\217\227\355\206\240\353\246\254/eval_per_event.csv"
+ M "results/loeo/B2/2000 \353\217\227\355\206\240\353\246\254/eval_scores.csv"
+ M "results/loeo/B2/2000 \353\217\227\355\206\240\353\246\254/eval_summary.csv"
+ M "results/loeo/B2/2000 \353\217\227\355\206\240\353\246\254/loss_curve.png"
+ M "results/loeo/B2/2000 \353\217\227\355\206\240\353\246\254/loss_history.csv"
+ M "results/loeo/B2/2000 \353\217\227\355\206\240\353\246\254/params.csv"
+ M "results/loeo/B2/2000 \353\217\227\355\206\240\353\246\254/predictions.csv"
+ M "results/loeo/B2/2000 \353\217\227\355\206\240\353\246\254/run_meta.json"
+ M "results/loeo/B2/2004 \353\213\210\352\260\200\355\203\200\355\230\204\354\243\274\354\227\220\354\223\260/eval_detail.csv"
+ M "results/loeo/B2/2004 \353\213\210\352\260\200\355\203\200\355\230\204\354\243\274\354\227\220\354\223\260/eval_per_event.csv"
+ M "results/loeo/B2/2004 \353\213\210\352\260\200\355\203\200\355\230\204\354\243\274\354\227\220\354\223\260/eval_scores.csv"
+ M "results/loeo/B2/2004 \353\213\210\352\260\200\355\203\200\355\230\204\354\243\274\354\227\220\354\223\260/eval_summary.csv"
+ M "results/loeo/B2/2004 \353\213\210\352\260\200\355\203\200\355\230\204\354\243\274\354\227\220\354\223\260/loss_curve.png"
+ M "results/loeo/B2/2004 \353\213\210\352\260\200\355\203\200\355\230\204\354\243\274\354\227\220\354\223\260/loss_history.csv"
+ M "results/loeo/B2/2004 \353\213\210\352\260\200\355\203\200\355\230\204\354\243\274\354\227\220\354\223\260/params.csv"
+ M "results/loeo/B2/2004 \353\213\210\352\260\200\355\203\200\355\230\204\354\243\274\354\227\220\354\223\260/predictions.csv"
+ M "results/loeo/B2/2004 \353\213\210\352\260\200\355\203\200\355\230\204\354\243\274\354\227\220\354\223\260/run_meta.json"
+ M "results/loeo/B2/2016 \352\265\254\353\247\210\353\252\250\355\206\240/eval_detail.csv"
+ M "results/loeo/B2/2016 \352\265\254\353\247\210\353\252\250\355\206\240/eval_per_event.csv"
+ M "results/loeo/B2/2016 \352\265\254\353\247\210\353\252\250\355\206\240/eval_scores.csv"
+ M "results/loeo/B2/2016 \352\265\254\353\247\210\353\252\250\355\206\240/eval_summary.csv"
+ M "results/loeo/B2/2016 \352\265\254\353\247\210\353\252\250\355\206\240/loss_curve.png"
+ M "results/loeo/B2/2016 \352\265\254\353\247\210\353\252\250\355\206\240/loss_history.csv"
+ M "results/loeo/B2/2016 \352\265\254\353\247\210\353\252\250\355\206\240/params.csv"
+ M "results/loeo/B2/2016 \352\265\254\353\247\210\353\252\250\355\206\240/predictions.csv"
+ M "results/loeo/B2/2016 \352\265\254\353\247\210\353\252\250\355\206\240/run_meta.json"
+ M "results/loeo/B2/2018 \354\230\244\354\202\254\354\271\264/eval_detail.csv"
+ M "results/loeo/B2/2018 \354\230\244\354\202\254\354\271\264/eval_per_event.csv"
+ M "results/loeo/B2/2018 \354\230\244\354\202\254\354\271\264/eval_scores.csv"
+ M "results/loeo/B2/2018 \354\230\244\354\202\254\354\271\264/eval_summary.csv"
+ M "results/loeo/B2/2018 \354\230\244\354\202\254\354\271\264/loss_curve.png"
+ M "results/loeo/B2/2018 \354\230\244\354\202\254\354\271\264/loss_history.csv"
+ M "results/loeo/B2/2018 \354\230\244\354\202\254\354\271\264/params.csv"
+ M "results/loeo/B2/2018 \354\230\244\354\202\254\354\271\264/predictions.csv"
+ M "results/loeo/B2/2018 \354\230\244\354\202\254\354\271\264/run_meta.json"
+ M "results/loeo/B2/2018 \355\233\227\354\271\264\354\235\264\353\217\204/eval_detail.csv"
+ M "results/loeo/B2/2018 \355\233\227\354\271\264\354\235\264\353\217\204/eval_per_event.csv"
+ M "results/loeo/B2/2018 \355\233\227\354\271\264\354\235\264\353\217\204/eval_scores.csv"
+ M "results/loeo/B2/2018 \355\233\227\354\271\264\354\235\264\353\217\204/eval_summary.csv"
+ M "results/loeo/B2/2018 \355\233\227\354\271\264\354\235\264\353\217\204/loss_curve.png"
+ M "results/loeo/B2/2018 \355\233\227\354\271\264\354\235\264\353\217\204/loss_history.csv"
+ M "results/loeo/B2/2018 \355\233\227\354\271\264\354\235\264\353\217\204/params.csv"
+ M "results/loeo/B2/2018 \355\233\227\354\271\264\354\235\264\353\217\204/predictions.csv"
+ M "results/loeo/B2/2018 \355\233\227\354\271\264\354\235\264\353\217\204/run_meta.json"
+ D "results/loeo/LOEO_\352\262\260\352\263\274.xlsx"
+ D "results/loeo/sheet_\353\266\200\355\212\270\354\212\244\355\212\270\353\236\251.csv"
+ D "results/loeo/sheet_\354\213\244\355\226\211\352\270\260\353\241\235.csv"
+ D "results/loeo/sheet_\354\232\224\354\225\275.csv"
+ D "results/loeo/sheet_\354\235\264\353\262\244\355\212\270\353\263\204.csv"
+ D "results/loeo/sheet_\354\236\254\355\230\204.csv"
+ D "results/loeo/sheet_\354\260\270\352\263\240\352\270\260\354\244\200\352\260\222.csv"
+ D "results/loeo/sheet_\355\232\214\354\260\250\353\263\204.csv"
+ M run_loeo.sh
+ M score_loeo.py
+ M train.py
+?? results/loeo/B0-logit/
+?? results/loeo/B2-logit/</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6022,7 +6241,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>주 조건은 지시서 §2-1 B 그대로 logit(pi) + log k. 기존 브랜치는 log(pi) + log k였고, 이것도 B0-log / B2-log로 함께 돌렸다</t>
+          <t>주 조건은 log(pi) + log k. 유도식 log lambda = log pi + log k 그대로이고 기존 면적 항 브랜치(followup3-area-avg-*)와 같다. 지시서 §2-1 B는 logit으로 적혀 있어 둘 다 돌렸는데 LS는 순위가 완전히 같고 (가중 AUC 0.8550 동일) LQ만 log가 앞서(0.7812 vs 0.7768) log를 주 조건으로 정했다. logit은 B0-logit / B2-logit으로 남긴다</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -6346,7 +6565,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --fix-b --out results/loeo/B0</t>
+          <t>train.py --prior-family area --area-link log --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --fix-b --out results/loeo/B0</t>
         </is>
       </c>
     </row>
@@ -6366,7 +6585,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --out results/loeo/B1</t>
+          <t>train.py --prior-family area --area-link log --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --out results/loeo/B1</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6605,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2000 돗토리 --out results/loeo/B2/2000 돗토리</t>
+          <t>train.py --prior-family area --area-link log --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2000 돗토리 --out results/loeo/B2/2000 돗토리</t>
         </is>
       </c>
     </row>
@@ -6406,7 +6625,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2004 니가타현주에쓰 --out results/loeo/B2/2004 니가타현주에쓰</t>
+          <t>train.py --prior-family area --area-link log --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2004 니가타현주에쓰 --out results/loeo/B2/2004 니가타현주에쓰</t>
         </is>
       </c>
     </row>
@@ -6426,7 +6645,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2016 구마모토 --out results/loeo/B2/2016 구마모토</t>
+          <t>train.py --prior-family area --area-link log --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2016 구마모토 --out results/loeo/B2/2016 구마모토</t>
         </is>
       </c>
     </row>
@@ -6446,7 +6665,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2018 오사카 --out results/loeo/B2/2018 오사카</t>
+          <t>train.py --prior-family area --area-link log --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2018 오사카 --out results/loeo/B2/2018 오사카</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6685,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2018 훗카이도 --out results/loeo/B2/2018 훗카이도</t>
+          <t>train.py --prior-family area --area-link log --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2018 훗카이도 --out results/loeo/B2/2018 훗카이도</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6705,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 1 --test-event 2000 돗토리 --out results/loeo/B2-w1/2000 돗토리</t>
+          <t>train.py --prior-family area --area-link log --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 1 --test-event 2000 돗토리 --out results/loeo/B2-w1/2000 돗토리</t>
         </is>
       </c>
     </row>
@@ -6506,7 +6725,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 1 --test-event 2004 니가타현주에쓰 --out results/loeo/B2-w1/2004 니가타현주에쓰</t>
+          <t>train.py --prior-family area --area-link log --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 1 --test-event 2004 니가타현주에쓰 --out results/loeo/B2-w1/2004 니가타현주에쓰</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6745,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 1 --test-event 2016 구마모토 --out results/loeo/B2-w1/2016 구마모토</t>
+          <t>train.py --prior-family area --area-link log --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 1 --test-event 2016 구마모토 --out results/loeo/B2-w1/2016 구마모토</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6765,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 1 --test-event 2018 오사카 --out results/loeo/B2-w1/2018 오사카</t>
+          <t>train.py --prior-family area --area-link log --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 1 --test-event 2018 오사카 --out results/loeo/B2-w1/2018 오사카</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6785,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 1 --test-event 2018 훗카이도 --out results/loeo/B2-w1/2018 훗카이도</t>
+          <t>train.py --prior-family area --area-link log --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 1 --test-event 2018 훗카이도 --out results/loeo/B2-w1/2018 훗카이도</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6805,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 10 --test-event 2000 돗토리 --out results/loeo/B2-w10/2000 돗토리</t>
+          <t>train.py --prior-family area --area-link log --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 10 --test-event 2000 돗토리 --out results/loeo/B2-w10/2000 돗토리</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6825,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 10 --test-event 2004 니가타현주에쓰 --out results/loeo/B2-w10/2004 니가타현주에쓰</t>
+          <t>train.py --prior-family area --area-link log --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 10 --test-event 2004 니가타현주에쓰 --out results/loeo/B2-w10/2004 니가타현주에쓰</t>
         </is>
       </c>
     </row>
@@ -6626,7 +6845,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 10 --test-event 2016 구마모토 --out results/loeo/B2-w10/2016 구마모토</t>
+          <t>train.py --prior-family area --area-link log --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 10 --test-event 2016 구마모토 --out results/loeo/B2-w10/2016 구마모토</t>
         </is>
       </c>
     </row>
@@ -6646,7 +6865,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 10 --test-event 2018 오사카 --out results/loeo/B2-w10/2018 오사카</t>
+          <t>train.py --prior-family area --area-link log --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 10 --test-event 2018 오사카 --out results/loeo/B2-w10/2018 오사카</t>
         </is>
       </c>
     </row>
@@ -6666,14 +6885,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 10 --test-event 2018 훗카이도 --out results/loeo/B2-w10/2018 훗카이도</t>
+          <t>train.py --prior-family area --area-link log --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 10 --test-event 2018 훗카이도 --out results/loeo/B2-w10/2018 훗카이도</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>실행 B0-log</t>
+          <t>실행 B0-logit</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6686,14 +6905,14 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --fix-b --area-link log --out results/loeo/B0-log</t>
+          <t>train.py --prior-family area --area-link logit --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --fix-b --out results/loeo/B0-logit</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>실행 B2-log</t>
+          <t>실행 B2-logit</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6706,14 +6925,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2000 돗토리 --area-link log --out results/loeo/B2-log/2000 돗토리</t>
+          <t>train.py --prior-family area --area-link logit --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2000 돗토리 --out results/loeo/B2-logit/2000 돗토리</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>실행 B2-log</t>
+          <t>실행 B2-logit</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6726,14 +6945,14 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2004 니가타현주에쓰 --area-link log --out results/loeo/B2-log/2004 니가타현주에쓰</t>
+          <t>train.py --prior-family area --area-link logit --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2004 니가타현주에쓰 --out results/loeo/B2-logit/2004 니가타현주에쓰</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>실행 B2-log</t>
+          <t>실행 B2-logit</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6746,14 +6965,14 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2016 구마모토 --area-link log --out results/loeo/B2-log/2016 구마모토</t>
+          <t>train.py --prior-family area --area-link logit --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2016 구마모토 --out results/loeo/B2-logit/2016 구마모토</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>실행 B2-log</t>
+          <t>실행 B2-logit</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6766,14 +6985,14 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2018 오사카 --area-link log --out results/loeo/B2-log/2018 오사카</t>
+          <t>train.py --prior-family area --area-link logit --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2018 오사카 --out results/loeo/B2-logit/2018 오사카</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>실행 B2-log</t>
+          <t>실행 B2-logit</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6786,7 +7005,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>train.py --prior-family area --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2018 훗카이도 --area-link log --out results/loeo/B2-log/2018 훗카이도</t>
+          <t>train.py --prior-family area --area-link logit --lam-gamma 10 --b-min -2 --b-max 4 --seed 0 --epochs 3000 --mtn-prior --ls-bce-weight 4.35 --test-event 2018 훗카이도 --out results/loeo/B2-logit/2018 훗카이도</t>
         </is>
       </c>
     </row>
